--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_326_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_326_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2125</v>
+        <v>4.9437</v>
       </c>
       <c r="E2" t="n">
         <v>2.9859</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2266</v>
+        <v>1.9578</v>
       </c>
       <c r="G2" t="n">
         <v>0.7917</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>1.346</v>
+        <v>1.0772</v>
       </c>
       <c r="T2" t="n">
         <v>-0.0272</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3733</v>
+        <v>1.1044</v>
       </c>
       <c r="V2" t="n">
         <v>3.0748</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.267</v>
+        <v>4.9233</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6429</v>
+        <v>4.9968</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3759</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>2.4645</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9502</v>
+        <v>-0.2939</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4274</v>
+        <v>-0.125</v>
       </c>
       <c r="V3" t="n">
         <v>3.2166</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7766</v>
+        <v>4.1819</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9139</v>
+        <v>4.7757</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8627</v>
+        <v>-0.5937</v>
       </c>
       <c r="G4" t="n">
-        <v>2.257</v>
+        <v>4.1897</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3168</v>
+        <v>1.359</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9402</v>
+        <v>2.8307</v>
       </c>
       <c r="J4" t="n">
-        <v>1.725</v>
+        <v>4.7834</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8856</v>
+        <v>1.9494</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1607</v>
+        <v>2.834</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5321</v>
+        <v>-0.5937</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5688</v>
+        <v>-0.5904</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1009</v>
+        <v>-0.0033</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3598</v>
+        <v>0.1366</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1889</v>
+        <v>-0.0077</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1709</v>
+        <v>0.1443</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.505</v>
+        <v>3.8267</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5313</v>
+        <v>1.7959</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9737</v>
+        <v>2.0307</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8377</v>
+        <v>2.257</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4994</v>
+        <v>1.3168</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3383</v>
+        <v>0.9402</v>
       </c>
       <c r="J5" t="n">
-        <v>2.896</v>
+        <v>1.725</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1329</v>
+        <v>1.8856</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7631</v>
+        <v>-0.1607</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0583</v>
+        <v>0.5321</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6335</v>
+        <v>-0.5688</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4248</v>
+        <v>1.1009</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>2.077</v>
+        <v>0.4099</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>0.0709</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1043</v>
+        <v>0.3389</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2225</v>
+        <v>2.564</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1859</v>
+        <v>1.5313</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9634</v>
+        <v>1.0327</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1897</v>
+        <v>1.8377</v>
       </c>
       <c r="H6" t="n">
-        <v>1.359</v>
+        <v>0.4994</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8307</v>
+        <v>1.3383</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7834</v>
+        <v>2.896</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9494</v>
+        <v>1.1329</v>
       </c>
       <c r="L6" t="n">
-        <v>2.834</v>
+        <v>1.7631</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5937</v>
+        <v>-1.0583</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5904</v>
+        <v>-0.6335</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0033</v>
+        <v>-0.4248</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8228</v>
+        <v>1.136</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5975</v>
+        <v>-0.0272</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2254</v>
+        <v>1.1633</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1477</v>
+        <v>0.9454</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2842</v>
+        <v>3.0483</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1365</v>
+        <v>-2.1029</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1146</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0303</v>
+        <v>-0.172</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2333</v>
+        <v>-0.1997</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6219</v>
+        <v>-0.2874</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1781</v>
+        <v>-0.8858</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0.7539</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0278</v>
+        <v>1.1185</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9831</v>
+        <v>0.2754</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0447</v>
+        <v>0.843</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6091</v>
+        <v>-0.5981</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3892</v>
+        <v>-1.4845</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7801</v>
+        <v>0.8863</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3711</v>
+        <v>-1.6213</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5007</v>
+        <v>-1.2531</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8704</v>
+        <v>-0.3682</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3878</v>
+        <v>-1.3314</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1113</v>
+        <v>-0.6519</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4991</v>
+        <v>-0.6794</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9833</v>
+        <v>-0.2899</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.612</v>
+        <v>-0.6012</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3713</v>
+        <v>0.3113</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4938</v>
+        <v>0.3273</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1098</v>
+        <v>0.0788</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6036</v>
+        <v>0.2484</v>
       </c>
       <c r="V9" t="n">
-        <v>2.428</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.428</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7826</v>
+        <v>-0.6763</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3665</v>
+        <v>-1.3892</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5839</v>
+        <v>0.7129</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6213</v>
+        <v>-2.3711</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2531</v>
+        <v>-0.5007</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3682</v>
+        <v>-1.8704</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3314</v>
+        <v>-1.3878</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6519</v>
+        <v>0.1113</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6794</v>
+        <v>-1.4991</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2899</v>
+        <v>-0.9833</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6012</v>
+        <v>-0.612</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3113</v>
+        <v>-0.3713</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1428</v>
+        <v>0.4266</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1968</v>
+        <v>-0.1098</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.054</v>
+        <v>0.5364</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1796</v>
+        <v>-1.574</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9075</v>
+        <v>-1.6716</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2721</v>
+        <v>0.0975</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7539</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6576</v>
+        <v>-0.0521</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>-0.3536</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.3016</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7525</v>
+        <v>-4.0385</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1936</v>
+        <v>-4.3115</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4411</v>
+        <v>0.273</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7122</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.282</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3791</v>
+        <v>0.2111</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6083</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5039</v>
+        <v>-4.2852</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1944</v>
+        <v>-2.0765</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3095</v>
+        <v>-2.2087</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8832</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3888</v>
+        <v>-0.17</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.925500000000003</v>
+        <v>9.925499999999996</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3148</v>
+        <v>7.314800000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6107</v>
+        <v>2.6105</v>
       </c>
       <c r="G14" t="n">
-        <v>1.838199999999998</v>
+        <v>1.8382</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.415100000000001</v>
+        <v>-3.4151</v>
       </c>
       <c r="I14" t="n">
-        <v>5.253100000000001</v>
+        <v>5.253099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>8.204300000000003</v>
+        <v>8.2043</v>
       </c>
       <c r="K14" t="n">
-        <v>2.650799999999998</v>
+        <v>2.650799999999999</v>
       </c>
       <c r="L14" t="n">
         <v>5.5534</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.3658</v>
+        <v>-6.365799999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.065600000000001</v>
+        <v>-6.065599999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3000999999999999</v>
+        <v>-0.3001</v>
       </c>
       <c r="P14" t="n">
         <v>-2.3195</v>
@@ -1546,13 +1546,13 @@
         <v>10.438</v>
       </c>
       <c r="S14" t="n">
-        <v>4.226100000000001</v>
+        <v>4.226099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3514000000000002</v>
+        <v>-0.3515</v>
       </c>
       <c r="U14" t="n">
-        <v>4.5776</v>
+        <v>4.5775</v>
       </c>
       <c r="V14" t="n">
         <v>6.1807</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8558</v>
+        <v>4.9129</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5509</v>
+        <v>2.7868</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3049</v>
+        <v>2.1261</v>
       </c>
       <c r="G15" t="n">
         <v>2.1966</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6449</v>
+        <v>-0.5878</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.187</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5421</v>
+        <v>0.3633</v>
       </c>
       <c r="V15" t="n">
         <v>2.1444</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5891</v>
+        <v>2.6905</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2899</v>
+        <v>1.5258</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2991</v>
+        <v>1.1647</v>
       </c>
       <c r="G16" t="n">
         <v>1.9986</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1054</v>
+        <v>-0.004</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3427</v>
+        <v>0.2082</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0569</v>
+        <v>1.6187</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6831</v>
+        <v>0.2113</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3739</v>
+        <v>1.4075</v>
       </c>
       <c r="G17" t="n">
         <v>0.6349</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7262</v>
+        <v>0.288</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4876</v>
+        <v>0.0158</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2385</v>
+        <v>0.2721</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5306999999999999</v>
+        <v>1.0583</v>
       </c>
       <c r="E18" t="n">
-        <v>1.256</v>
+        <v>1.4919</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.4336</v>
       </c>
       <c r="G18" t="n">
         <v>1.5233</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2942</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9709</v>
+        <v>-0.735</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3233</v>
+        <v>-0.0316</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3943</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1421</v>
+        <v>-0.2267</v>
       </c>
       <c r="E19" t="n">
-        <v>2.628</v>
+        <v>2.423</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7702</v>
+        <v>-2.6498</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7952</v>
+        <v>1.2012</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5651</v>
+        <v>0.7527</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7699</v>
+        <v>0.4484</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5138</v>
+        <v>2.7413</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4402</v>
+        <v>0.9747</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0736</v>
+        <v>1.7666</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7186</v>
+        <v>-1.5401</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1249</v>
+        <v>-0.222</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8435</v>
+        <v>-1.3182</v>
       </c>
       <c r="P19" t="n">
         <v>1.1598</v>
@@ -1936,22 +1936,22 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5834</v>
+        <v>-0.4433</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1142</v>
+        <v>-0.3183</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4692</v>
+        <v>-0.125</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.6805</v>
+        <v>-2.1444</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6805</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6451</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9649</v>
+        <v>-1.3187</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3198</v>
+        <v>0.7123</v>
       </c>
       <c r="G20" t="n">
         <v>-0.08069999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4406</v>
+        <v>-0.402</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1845</v>
+        <v>-0.5384</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2561</v>
+        <v>0.1364</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8197</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.883</v>
+        <v>-0.7261</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0692</v>
+        <v>-1.8817</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9522</v>
+        <v>1.1556</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2012</v>
+        <v>-1.2116</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7527</v>
+        <v>-1.9376</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4484</v>
+        <v>0.7261</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7413</v>
+        <v>-0.9964</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9747</v>
+        <v>-1.4614</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7666</v>
+        <v>0.465</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5401</v>
+        <v>-0.2152</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.222</v>
+        <v>-0.4762</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3182</v>
+        <v>0.261</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0996</v>
+        <v>-0.5867</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6721</v>
+        <v>-0.5658</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4274</v>
+        <v>-0.0209</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5904</v>
+        <v>-0.7648</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3535</v>
+        <v>2.2742</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7631</v>
+        <v>-3.039</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2116</v>
+        <v>0.7952</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9376</v>
+        <v>2.5651</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7261</v>
+        <v>-1.7699</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9964</v>
+        <v>2.5138</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4614</v>
+        <v>2.4402</v>
       </c>
       <c r="L22" t="n">
-        <v>0.465</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2152</v>
+        <v>-1.7186</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4762</v>
+        <v>0.1249</v>
       </c>
       <c r="O22" t="n">
-        <v>0.261</v>
+        <v>-1.8435</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.451</v>
+        <v>-0.0393</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0376</v>
+        <v>-0.2396</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4134</v>
+        <v>0.2003</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0722</v>
+        <v>-2.6805</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8155</v>
+        <v>-2.3552</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8879</v>
+        <v>-1.5956</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9276</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0.5095</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3835</v>
+        <v>-0.1562</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6844</v>
+        <v>-0.0233</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3009</v>
+        <v>-0.1329</v>
       </c>
       <c r="V23" t="n">
         <v>1.4665</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1194</v>
+        <v>-3.8663</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2028</v>
+        <v>-1.8489</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9166</v>
+        <v>-2.0174</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2144</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2245</v>
+        <v>0.0286</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3651</v>
+        <v>0.2642</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6083</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7723</v>
+        <v>-5.3779</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0336</v>
+        <v>-3.2695</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7386</v>
+        <v>-2.1083</v>
       </c>
       <c r="G25" t="n">
         <v>-3.4299</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.284</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2715</v>
+        <v>0.0356</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6181</v>
+        <v>0.2484</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.9901</v>
+        <v>-5.4961</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6449</v>
+        <v>-3.409</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3452</v>
+        <v>-2.0871</v>
       </c>
       <c r="G26" t="n">
         <v>-2.7611</v>
@@ -2482,13 +2482,13 @@
         <v>0.6959</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5485</v>
+        <v>-1.0545</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0455</v>
+        <v>-0.8096</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.503</v>
+        <v>-0.2449</v>
       </c>
       <c r="V26" t="n">
         <v>-2.1444</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.9254</v>
+        <v>-9.139099999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.6105</v>
+        <v>-2.6104</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.3149</v>
+        <v>-6.528600000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-1.838399999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4148</v>
+        <v>3.414799999999999</v>
       </c>
       <c r="I27" t="n">
         <v>-5.2531</v>
@@ -2560,13 +2560,13 @@
         <v>12.7576</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.225999999999999</v>
+        <v>-3.4398</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.577500000000001</v>
+        <v>-4.577599999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3516</v>
+        <v>1.1376</v>
       </c>
       <c r="V27" t="n">
         <v>-6.180700000000001</v>
